--- a/data/trans_orig/P57GLOBAL_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57GLOBAL_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2007</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>277873</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>321885</t>
+          <t>323103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>274172</t>
+          <t>273667</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>314419</t>
+          <t>315562</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>565063</t>
+          <t>565751</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>625030</t>
+          <t>625298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171342</t>
+          <t>170124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215354</t>
+          <t>213911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>153070</t>
+          <t>151927</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>193317</t>
+          <t>193822</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>335686</t>
+          <t>335418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>395653</t>
+          <t>394965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>472355</t>
+          <t>472737</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>525543</t>
+          <t>524808</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>409696</t>
+          <t>411091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>454622</t>
+          <t>456299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>899465</t>
+          <t>896579</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>967031</t>
+          <t>966954</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>209946</t>
+          <t>210681</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>263134</t>
+          <t>262752</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>168726</t>
+          <t>167049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>213652</t>
+          <t>212257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391806</t>
+          <t>391883</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>459372</t>
+          <t>462258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>425541</t>
+          <t>425266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>470287</t>
+          <t>470862</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>464503</t>
+          <t>463526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>511466</t>
+          <t>512986</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>905313</t>
+          <t>905963</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>971707</t>
+          <t>969986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167296</t>
+          <t>166721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>212042</t>
+          <t>212317</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177298</t>
+          <t>175778</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224261</t>
+          <t>225238</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>354640</t>
+          <t>356361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>421034</t>
+          <t>420384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>355174</t>
+          <t>354309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>397220</t>
+          <t>397825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>345761</t>
+          <t>346838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>388251</t>
+          <t>387186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>715805</t>
+          <t>714336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>772290</t>
+          <t>774286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120377</t>
+          <t>119772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162423</t>
+          <t>163288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>127391</t>
+          <t>128456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169881</t>
+          <t>168804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260949</t>
+          <t>258953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>317434</t>
+          <t>318903</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>262167</t>
+          <t>259978</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>295773</t>
+          <t>296220</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>295589</t>
+          <t>295981</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>328078</t>
+          <t>329775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>567990</t>
+          <t>564501</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>615941</t>
+          <t>615888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90093</t>
+          <t>89646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123699</t>
+          <t>125888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75908</t>
+          <t>74211</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108397</t>
+          <t>108005</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173911</t>
+          <t>173964</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>221862</t>
+          <t>225351</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>212445</t>
+          <t>212443</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>239303</t>
+          <t>240991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>255587</t>
+          <t>253065</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>283251</t>
+          <t>282512</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>474943</t>
+          <t>475490</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>515070</t>
+          <t>516414</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,48%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51529</t>
+          <t>49841</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78387</t>
+          <t>78389</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59683</t>
+          <t>60422</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87347</t>
+          <t>89869</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118696</t>
+          <t>117352</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>158823</t>
+          <t>158276</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>158372</t>
+          <t>158393</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>180205</t>
+          <t>180891</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>257219</t>
+          <t>256981</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>286488</t>
+          <t>286644</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>424163</t>
+          <t>423895</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>462680</t>
+          <t>461741</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29678</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51511</t>
+          <t>51490</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47420</t>
+          <t>47264</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76689</t>
+          <t>76927</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>81111</t>
+          <t>82050</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>119628</t>
+          <t>119896</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2250542</t>
+          <t>2250039</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2354164</t>
+          <t>2355032</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2385333</t>
+          <t>2385562</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2485211</t>
+          <t>2491086</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4661791</t>
+          <t>4665905</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4811229</t>
+          <t>4815066</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,44%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>916312</t>
+          <t>915444</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1019934</t>
+          <t>1020437</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>890860</t>
+          <t>884985</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>990738</t>
+          <t>990509</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1835319</t>
+          <t>1831482</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1984757</t>
+          <t>1980643</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2012</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2012 (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>249567</t>
+          <t>250840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>291870</t>
+          <t>294142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>262831</t>
+          <t>261054</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>300424</t>
+          <t>299491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>525206</t>
+          <t>526585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>583404</t>
+          <t>580470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>156385</t>
+          <t>154113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>198688</t>
+          <t>197415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126870</t>
+          <t>127803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164463</t>
+          <t>166240</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>292145</t>
+          <t>295079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>348964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>418444</t>
+          <t>419253</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>467667</t>
+          <t>469068</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>418689</t>
+          <t>420016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>464535</t>
+          <t>464391</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>853390</t>
+          <t>853010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>922239</t>
+          <t>920845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,5%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212199</t>
+          <t>210798</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>261422</t>
+          <t>260613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>143568</t>
+          <t>143712</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>189414</t>
+          <t>188087</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>365730</t>
+          <t>367124</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>434579</t>
+          <t>434959</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>459054</t>
+          <t>462823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>508604</t>
+          <t>508458</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>508991</t>
+          <t>506878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>555731</t>
+          <t>555553</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>984979</t>
+          <t>982118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1050166</t>
+          <t>1050107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168243</t>
+          <t>168389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>217793</t>
+          <t>214024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147750</t>
+          <t>147928</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>194490</t>
+          <t>196603</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>330161</t>
+          <t>330220</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>395348</t>
+          <t>398209</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>405149</t>
+          <t>405810</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452327</t>
+          <t>453265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>469171</t>
+          <t>469707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>509861</t>
+          <t>509495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>884869</t>
+          <t>886878</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>953039</t>
+          <t>950362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156155</t>
+          <t>155217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203333</t>
+          <t>202672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100503</t>
+          <t>100869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141193</t>
+          <t>140657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>265807</t>
+          <t>268484</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>333977</t>
+          <t>331968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>264091</t>
+          <t>262992</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>305301</t>
+          <t>303529</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>312051</t>
+          <t>314973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>350526</t>
+          <t>351762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>592802</t>
+          <t>591946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>647514</t>
+          <t>646063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,35%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118882</t>
+          <t>120654</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160092</t>
+          <t>161191</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>94197</t>
+          <t>92961</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132672</t>
+          <t>129750</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>221393</t>
+          <t>222844</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276105</t>
+          <t>276961</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>209732</t>
+          <t>209140</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>240556</t>
+          <t>240432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>252369</t>
+          <t>252620</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>282777</t>
+          <t>283803</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>471507</t>
+          <t>473533</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>516249</t>
+          <t>515894</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,3%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62540</t>
+          <t>62664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93364</t>
+          <t>93956</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>63697</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95131</t>
+          <t>94880</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134348</t>
+          <t>134703</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179090</t>
+          <t>177064</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>176051</t>
+          <t>174755</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>203304</t>
+          <t>203206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>286144</t>
+          <t>285171</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>318417</t>
+          <t>317736</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>469137</t>
+          <t>471438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>513831</t>
+          <t>512714</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42318</t>
+          <t>42416</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69571</t>
+          <t>70867</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>63021</t>
+          <t>63702</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>95294</t>
+          <t>96267</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>113229</t>
+          <t>114346</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>157923</t>
+          <t>155622</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2280017</t>
+          <t>2278392</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2384626</t>
+          <t>2391339</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2596683</t>
+          <t>2599356</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2703225</t>
+          <t>2702639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4901721</t>
+          <t>4910688</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5060829</t>
+          <t>5064090</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1001726</t>
+          <t>995013</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1106335</t>
+          <t>1107960</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>819678</t>
+          <t>820264</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>926220</t>
+          <t>923547</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1848426</t>
+          <t>1845165</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2007534</t>
+          <t>1998567</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2016</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2016 (tasa de respuesta: 99,15%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>308884</t>
+          <t>306856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>342324</t>
+          <t>342816</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>297712</t>
+          <t>297131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>328593</t>
+          <t>329664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>613584</t>
+          <t>615979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>664266</t>
+          <t>662558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77139</t>
+          <t>76647</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>110579</t>
+          <t>112607</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66200</t>
+          <t>65129</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97081</t>
+          <t>97662</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149990</t>
+          <t>151698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200672</t>
+          <t>198277</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>452441</t>
+          <t>453930</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>490780</t>
+          <t>491254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>435498</t>
+          <t>435346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>470589</t>
+          <t>470588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>900456</t>
+          <t>899571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952478</t>
+          <t>950270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,38%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89627</t>
+          <t>89153</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127966</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88655</t>
+          <t>88656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>123746</t>
+          <t>123898</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>187173</t>
+          <t>189381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>239195</t>
+          <t>240080</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>528161</t>
+          <t>528735</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>567841</t>
+          <t>568894</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>517237</t>
+          <t>516097</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>556137</t>
+          <t>553876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1056803</t>
+          <t>1057940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1112965</t>
+          <t>1113072</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100390</t>
+          <t>99337</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140070</t>
+          <t>139496</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94051</t>
+          <t>96312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132951</t>
+          <t>134091</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>205454</t>
+          <t>205347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>261616</t>
+          <t>260479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>503007</t>
+          <t>505013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>544768</t>
+          <t>544781</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>530700</t>
+          <t>531577</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>567458</t>
+          <t>568832</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1047111</t>
+          <t>1049940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1101911</t>
+          <t>1104833</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,17%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94148</t>
+          <t>94135</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135909</t>
+          <t>133903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75840</t>
+          <t>74466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112598</t>
+          <t>111721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>180303</t>
+          <t>177381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>235103</t>
+          <t>232274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>377294</t>
+          <t>375555</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>411032</t>
+          <t>410080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>407535</t>
+          <t>407605</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>440256</t>
+          <t>440091</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>795763</t>
+          <t>795313</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>842254</t>
+          <t>842998</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62436</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95222</t>
+          <t>96961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49760</t>
+          <t>49925</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82481</t>
+          <t>82411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120277</t>
+          <t>119533</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>166768</t>
+          <t>167218</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>252428</t>
+          <t>251734</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>281905</t>
+          <t>281893</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>324732</t>
+          <t>323821</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>347643</t>
+          <t>347476</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>583259</t>
+          <t>585316</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>622391</t>
+          <t>621988</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50420</t>
+          <t>50432</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79897</t>
+          <t>80591</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>26228</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48972</t>
+          <t>49883</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83638</t>
+          <t>84041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122770</t>
+          <t>120713</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>208404</t>
+          <t>208064</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>228721</t>
+          <t>228741</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>343775</t>
+          <t>343436</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>370197</t>
+          <t>369605</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>558629</t>
+          <t>559651</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>593236</t>
+          <t>594387</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27412</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47729</t>
+          <t>48069</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53747</t>
+          <t>54086</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>59268</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>95026</t>
+          <t>94004</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2717762</t>
+          <t>2709949</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2808146</t>
+          <t>2805215</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,82 +9107,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>83,29%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2788</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>2975000</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2929722</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3018733</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>84,79%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>83,5%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>86,03%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>5414</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>5733599</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>5672689</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>5791798</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>83,38%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2788</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2975000</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2924839</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3015188</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>84,79%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>83,36%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>85,93%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>5414</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>5733599</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>5669921</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>5799050</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>83,38%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>559846</t>
+          <t>562777</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>650230</t>
+          <t>658043</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,82 +9220,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>16,71%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>19,54%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>533764</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>490031</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>579042</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>13,97%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1143157</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1084958</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1204067</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>16,62%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>533764</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>493576</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>583925</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>14,07%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1143157</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1077706</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1206835</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>16,62%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2023</t>
+          <t>Población con apoyo social funcional bajo, por encima del percentil 15 (Duke) en 2023 (tasa de respuesta: 98,07%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148318</t>
+          <t>147864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>217263</t>
+          <t>216368</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>127012</t>
+          <t>124064</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173903</t>
+          <t>173800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>287406</t>
+          <t>291946</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>372348</t>
+          <t>375164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>178478</t>
+          <t>179373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>247423</t>
+          <t>247877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131229</t>
+          <t>131332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>178120</t>
+          <t>181068</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>328525</t>
+          <t>325709</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>413467</t>
+          <t>408927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,35%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>234501</t>
+          <t>236061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>288538</t>
+          <t>289401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160442</t>
+          <t>149055</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289519</t>
+          <t>288627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>376657</t>
+          <t>396596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>558254</t>
+          <t>557856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132272</t>
+          <t>131409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>186309</t>
+          <t>184749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218996</t>
+          <t>219888</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348073</t>
+          <t>359460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>371071</t>
+          <t>371469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>552668</t>
+          <t>532729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>311335</t>
+          <t>309785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>358278</t>
+          <t>354777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>307654</t>
+          <t>309299</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>347534</t>
+          <t>347373</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>634319</t>
+          <t>630743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>692487</t>
+          <t>690121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,6%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>170499</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>217442</t>
+          <t>218992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191943</t>
+          <t>192104</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231823</t>
+          <t>230178</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>375767</t>
+          <t>378133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>433935</t>
+          <t>437511</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>180597</t>
+          <t>165931</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>563607</t>
+          <t>565903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>376400</t>
+          <t>354545</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>468604</t>
+          <t>466871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>504994</t>
+          <t>524314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1012307</t>
+          <t>1005841</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,78%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>313652</t>
+          <t>311356</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>696662</t>
+          <t>711328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231294</t>
+          <t>233027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323498</t>
+          <t>345353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>564850</t>
+          <t>571316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1072163</t>
+          <t>1052843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>66,76%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>357896</t>
+          <t>358774</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>400027</t>
+          <t>398692</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>373583</t>
+          <t>372410</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>404424</t>
+          <t>404235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>741866</t>
+          <t>743027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>792641</t>
+          <t>794285</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,96%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154223</t>
+          <t>155558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196354</t>
+          <t>195476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130018</t>
+          <t>130207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160859</t>
+          <t>162032</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296051</t>
+          <t>294407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>346826</t>
+          <t>345665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>227221</t>
+          <t>229592</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>258188</t>
+          <t>259505</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>249482</t>
+          <t>249135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>276259</t>
+          <t>274939</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>485761</t>
+          <t>487102</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>525130</t>
+          <t>525633</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,74%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>105249</t>
+          <t>103932</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136216</t>
+          <t>133845</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113967</t>
+          <t>115287</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140744</t>
+          <t>141091</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>228533</t>
+          <t>228030</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>267902</t>
+          <t>266561</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,37%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183144</t>
+          <t>183074</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>207003</t>
+          <t>206445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>299079</t>
+          <t>299137</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>323557</t>
+          <t>323513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>490324</t>
+          <t>489099</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>523944</t>
+          <t>523289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>63742</t>
+          <t>64300</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87601</t>
+          <t>87671</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88711</t>
+          <t>88755</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>113189</t>
+          <t>113131</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>159069</t>
+          <t>159724</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>192689</t>
+          <t>193914</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1518941</t>
+          <t>1494593</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2174881</t>
+          <t>2170174</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1980925</t>
+          <t>1955444</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2201273</t>
+          <t>2194019</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3520377</t>
+          <t>3527222</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4320061</t>
+          <t>4322024</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1236137</t>
+          <t>1240844</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1892077</t>
+          <t>1916425</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1188685</t>
+          <t>1195939</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1409033</t>
+          <t>1434514</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2480916</t>
+          <t>2478953</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3280600</t>
+          <t>3273755</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57GLOBAL_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57GLOBAL_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>279316</t>
+          <t>280634</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>323103</t>
+          <t>324388</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>315562</t>
+          <t>314662</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>565751</t>
+          <t>567861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>625298</t>
+          <t>627446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>170124</t>
+          <t>168839</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213911</t>
+          <t>212593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151927</t>
+          <t>152827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>335418</t>
+          <t>333270</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>394965</t>
+          <t>392855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>472737</t>
+          <t>472277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>524808</t>
+          <t>524702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>411091</t>
+          <t>407515</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>456299</t>
+          <t>455177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>896579</t>
+          <t>895088</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>966954</t>
+          <t>966699</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>210681</t>
+          <t>210787</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262752</t>
+          <t>263212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167049</t>
+          <t>168171</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>212257</t>
+          <t>215833</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391883</t>
+          <t>392138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>462258</t>
+          <t>463749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>425266</t>
+          <t>421793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>470862</t>
+          <t>469930</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>463526</t>
+          <t>465425</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>512986</t>
+          <t>513767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>905963</t>
+          <t>904819</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>969986</t>
+          <t>971835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,27%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>166721</t>
+          <t>167653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>212317</t>
+          <t>215790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>175778</t>
+          <t>174997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>225238</t>
+          <t>223339</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>356361</t>
+          <t>354512</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>420384</t>
+          <t>421528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>354309</t>
+          <t>355903</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>397825</t>
+          <t>397644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>346838</t>
+          <t>346908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>387186</t>
+          <t>389480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>714336</t>
+          <t>715165</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>774286</t>
+          <t>776396</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119772</t>
+          <t>119953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163288</t>
+          <t>161694</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128456</t>
+          <t>126162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>168804</t>
+          <t>168734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258953</t>
+          <t>256843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318903</t>
+          <t>318074</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,78%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>259978</t>
+          <t>261008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>296220</t>
+          <t>296583</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>295981</t>
+          <t>294282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>329775</t>
+          <t>328266</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>564501</t>
+          <t>567079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>615888</t>
+          <t>616141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89646</t>
+          <t>89283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>125888</t>
+          <t>124858</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74211</t>
+          <t>75720</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>108005</t>
+          <t>109704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173964</t>
+          <t>173711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225351</t>
+          <t>222773</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>212443</t>
+          <t>211548</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>240991</t>
+          <t>239303</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>253065</t>
+          <t>254025</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>282512</t>
+          <t>283181</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>475490</t>
+          <t>474566</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>516414</t>
+          <t>514557</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49841</t>
+          <t>51529</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78389</t>
+          <t>79284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60422</t>
+          <t>59753</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89869</t>
+          <t>88909</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117352</t>
+          <t>119209</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>158276</t>
+          <t>159200</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>158393</t>
+          <t>158260</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>180891</t>
+          <t>180133</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>256981</t>
+          <t>259249</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>286644</t>
+          <t>287911</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>423895</t>
+          <t>427209</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>461741</t>
+          <t>461943</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,95%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28992</t>
+          <t>29750</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>51490</t>
+          <t>51623</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47264</t>
+          <t>45997</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76927</t>
+          <t>74659</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>82050</t>
+          <t>81848</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>119896</t>
+          <t>116582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2250039</t>
+          <t>2246459</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2355032</t>
+          <t>2354550</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2385562</t>
+          <t>2391150</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2491086</t>
+          <t>2493440</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4665905</t>
+          <t>4670773</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4815066</t>
+          <t>4816316</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>915444</t>
+          <t>915926</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1020437</t>
+          <t>1024017</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>884985</t>
+          <t>882631</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>990509</t>
+          <t>984921</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1831482</t>
+          <t>1830232</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1980643</t>
+          <t>1975775</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>250840</t>
+          <t>250946</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>294142</t>
+          <t>294390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>261054</t>
+          <t>259175</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>299491</t>
+          <t>298164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>526585</t>
+          <t>526689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>580470</t>
+          <t>584316</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>154113</t>
+          <t>153865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>197415</t>
+          <t>197309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127803</t>
+          <t>129130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>166240</t>
+          <t>168119</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>295079</t>
+          <t>291233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>348964</t>
+          <t>348860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>419253</t>
+          <t>415227</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>469068</t>
+          <t>466816</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>420016</t>
+          <t>419475</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>463645</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>853010</t>
+          <t>853201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>920845</t>
+          <t>920170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,44%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>210798</t>
+          <t>213050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>260613</t>
+          <t>264639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>143712</t>
+          <t>144458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>188087</t>
+          <t>188628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>367124</t>
+          <t>367799</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>434959</t>
+          <t>434768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>462823</t>
+          <t>459193</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>508458</t>
+          <t>509112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>506878</t>
+          <t>506997</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>555553</t>
+          <t>554777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>982118</t>
+          <t>981222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1050107</t>
+          <t>1049072</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168389</t>
+          <t>167735</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>214024</t>
+          <t>217654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147928</t>
+          <t>148704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196603</t>
+          <t>196484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>330220</t>
+          <t>331255</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>398209</t>
+          <t>399105</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>405810</t>
+          <t>404781</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>453265</t>
+          <t>453215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>469707</t>
+          <t>467517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>509495</t>
+          <t>508944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>886878</t>
+          <t>886171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>950362</t>
+          <t>948716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155217</t>
+          <t>155267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202672</t>
+          <t>203701</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100869</t>
+          <t>101420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140657</t>
+          <t>142847</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>268484</t>
+          <t>270130</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331968</t>
+          <t>332675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,29%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>262992</t>
+          <t>264030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>303529</t>
+          <t>304339</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>314973</t>
+          <t>313752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>351762</t>
+          <t>352162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>591946</t>
+          <t>588462</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>646063</t>
+          <t>645223</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120654</t>
+          <t>119844</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161191</t>
+          <t>160153</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92961</t>
+          <t>92561</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129750</t>
+          <t>130971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>222844</t>
+          <t>223684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276961</t>
+          <t>280445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>209140</t>
+          <t>210119</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>240432</t>
+          <t>240946</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>252620</t>
+          <t>254924</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>283803</t>
+          <t>284933</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>473533</t>
+          <t>472823</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>515894</t>
+          <t>516920</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62664</t>
+          <t>62150</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93956</t>
+          <t>92977</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63697</t>
+          <t>62567</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>94880</t>
+          <t>92576</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>134703</t>
+          <t>133677</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177064</t>
+          <t>177774</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>174755</t>
+          <t>176738</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>203206</t>
+          <t>203309</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>285171</t>
+          <t>285032</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>317736</t>
+          <t>317118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>471438</t>
+          <t>469151</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>512714</t>
+          <t>513285</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42416</t>
+          <t>42313</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70867</t>
+          <t>68884</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>63702</t>
+          <t>64320</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>96267</t>
+          <t>96406</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>114346</t>
+          <t>113775</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>155622</t>
+          <t>157909</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2278392</t>
+          <t>2276496</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2391339</t>
+          <t>2387681</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2599356</t>
+          <t>2603273</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2702639</t>
+          <t>2701715</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4910688</t>
+          <t>4908312</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5064090</t>
+          <t>5063081</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>995013</t>
+          <t>998671</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1107960</t>
+          <t>1109856</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>820264</t>
+          <t>821188</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>923547</t>
+          <t>919630</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1845165</t>
+          <t>1846174</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1998567</t>
+          <t>2000943</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>306856</t>
+          <t>310408</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>342816</t>
+          <t>343800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>297131</t>
+          <t>298774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>329664</t>
+          <t>328887</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>615979</t>
+          <t>615464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>662558</t>
+          <t>661798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76647</t>
+          <t>75663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112607</t>
+          <t>109055</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65129</t>
+          <t>65906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97662</t>
+          <t>96019</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151698</t>
+          <t>152458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198277</t>
+          <t>198792</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>453930</t>
+          <t>453123</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>491254</t>
+          <t>490085</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>435346</t>
+          <t>431946</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>470588</t>
+          <t>468852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>899571</t>
+          <t>899728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>950270</t>
+          <t>951981</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89153</t>
+          <t>90322</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126477</t>
+          <t>127284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88656</t>
+          <t>90392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>123898</t>
+          <t>127298</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189381</t>
+          <t>187670</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>240080</t>
+          <t>239923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>528735</t>
+          <t>528772</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>568894</t>
+          <t>569379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>516097</t>
+          <t>515508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>553876</t>
+          <t>553577</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1057940</t>
+          <t>1058989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1113072</t>
+          <t>1113324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99337</t>
+          <t>98852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139496</t>
+          <t>139459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96312</t>
+          <t>96611</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134091</t>
+          <t>134680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>205347</t>
+          <t>205095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>260479</t>
+          <t>259430</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>505013</t>
+          <t>505606</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>544781</t>
+          <t>545486</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>531577</t>
+          <t>531321</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>568832</t>
+          <t>565077</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1049940</t>
+          <t>1047528</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1104833</t>
+          <t>1103563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94135</t>
+          <t>93430</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133903</t>
+          <t>133310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74466</t>
+          <t>78221</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111721</t>
+          <t>111977</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>177381</t>
+          <t>178651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232274</t>
+          <t>234686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>375555</t>
+          <t>377462</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>410080</t>
+          <t>411518</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>407605</t>
+          <t>406850</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>440091</t>
+          <t>439018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>795313</t>
+          <t>795056</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>842998</t>
+          <t>842662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62436</t>
+          <t>60998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96961</t>
+          <t>95054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49925</t>
+          <t>50998</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82411</t>
+          <t>83166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>119533</t>
+          <t>119869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>167218</t>
+          <t>167475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>251734</t>
+          <t>251813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>281893</t>
+          <t>281908</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>323821</t>
+          <t>323419</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>347476</t>
+          <t>347532</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>585316</t>
+          <t>584849</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>621988</t>
+          <t>622161</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50432</t>
+          <t>50417</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>80591</t>
+          <t>80512</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26228</t>
+          <t>26172</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49883</t>
+          <t>50285</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>84041</t>
+          <t>83868</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>120713</t>
+          <t>121180</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>208064</t>
+          <t>208801</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>228741</t>
+          <t>228264</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>343436</t>
+          <t>342733</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>369605</t>
+          <t>370237</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>559651</t>
+          <t>556536</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>594387</t>
+          <t>592241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48069</t>
+          <t>47332</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27917</t>
+          <t>27285</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54086</t>
+          <t>54789</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59268</t>
+          <t>61414</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94004</t>
+          <t>97119</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2709949</t>
+          <t>2710225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2805215</t>
+          <t>2804228</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2929722</t>
+          <t>2925991</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3018733</t>
+          <t>3014856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5672689</t>
+          <t>5663488</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5791798</t>
+          <t>5792360</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>562777</t>
+          <t>563764</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>658043</t>
+          <t>657767</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>490031</t>
+          <t>493908</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>579042</t>
+          <t>582773</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1084958</t>
+          <t>1084396</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1204067</t>
+          <t>1213268</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>181907</t>
+          <t>192829</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>147864</t>
+          <t>157330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>216368</t>
+          <t>224661</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>149340</t>
+          <t>183204</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124064</t>
+          <t>157206</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>173800</t>
+          <t>209369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>331246</t>
+          <t>376033</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>291946</t>
+          <t>333137</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>375164</t>
+          <t>415919</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>213834</t>
+          <t>210458</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>179373</t>
+          <t>178626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>247877</t>
+          <t>245957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>155792</t>
+          <t>171412</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>131332</t>
+          <t>145247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181068</t>
+          <t>197410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>369627</t>
+          <t>381871</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>325709</t>
+          <t>341985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>408927</t>
+          <t>424767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>395741</t>
+          <t>403287</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>395741</t>
+          <t>403287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>395741</t>
+          <t>403287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>305132</t>
+          <t>354616</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>305132</t>
+          <t>354616</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>305132</t>
+          <t>354616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>700873</t>
+          <t>757904</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>700873</t>
+          <t>757904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>700873</t>
+          <t>757904</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>263560</t>
+          <t>304905</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>236061</t>
+          <t>275774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>289401</t>
+          <t>330749</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>241730</t>
+          <t>281623</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>149055</t>
+          <t>257332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>288627</t>
+          <t>305127</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>505290</t>
+          <t>586529</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>396596</t>
+          <t>549596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>557856</t>
+          <t>624456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>64,35%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>157250</t>
+          <t>169181</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>131409</t>
+          <t>143337</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184749</t>
+          <t>198312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>266785</t>
+          <t>214716</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219888</t>
+          <t>191212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359460</t>
+          <t>239007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>424035</t>
+          <t>383897</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>371469</t>
+          <t>345970</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>532729</t>
+          <t>420830</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>420810</t>
+          <t>474086</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>420810</t>
+          <t>474086</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>420810</t>
+          <t>474086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>508515</t>
+          <t>496339</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>508515</t>
+          <t>496339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>508515</t>
+          <t>496339</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>929325</t>
+          <t>970426</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>929325</t>
+          <t>970426</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>929325</t>
+          <t>970426</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>333319</t>
+          <t>397931</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>309785</t>
+          <t>372906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>354777</t>
+          <t>424259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>328152</t>
+          <t>387038</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>309299</t>
+          <t>365530</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>347373</t>
+          <t>407696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>661471</t>
+          <t>784968</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>630743</t>
+          <t>751381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>690121</t>
+          <t>817582</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>195458</t>
+          <t>212712</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>174000</t>
+          <t>186384</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218992</t>
+          <t>237737</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>211325</t>
+          <t>231429</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>192104</t>
+          <t>210771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>230178</t>
+          <t>252937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>406783</t>
+          <t>444142</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378133</t>
+          <t>411528</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>437511</t>
+          <t>477729</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>528777</t>
+          <t>610643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>528777</t>
+          <t>610643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>528777</t>
+          <t>610643</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>539477</t>
+          <t>618467</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>539477</t>
+          <t>618467</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>539477</t>
+          <t>618467</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1068254</t>
+          <t>1229110</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1068254</t>
+          <t>1229110</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1068254</t>
+          <t>1229110</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>398969</t>
+          <t>439642</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>165931</t>
+          <t>412323</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>565903</t>
+          <t>463690</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>437911</t>
+          <t>477288</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>354545</t>
+          <t>454231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>466871</t>
+          <t>496354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>836880</t>
+          <t>916930</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>524314</t>
+          <t>886202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1005841</t>
+          <t>949443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>67,26%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>478290</t>
+          <t>249208</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>311356</t>
+          <t>225160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>711328</t>
+          <t>276527</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>261987</t>
+          <t>245517</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>233027</t>
+          <t>226451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>345353</t>
+          <t>268574</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>740277</t>
+          <t>494725</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>571316</t>
+          <t>462212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1052843</t>
+          <t>525453</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>37,22%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>877259</t>
+          <t>688850</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>877259</t>
+          <t>688850</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>877259</t>
+          <t>688850</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>699898</t>
+          <t>722805</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>699898</t>
+          <t>722805</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>699898</t>
+          <t>722805</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1577157</t>
+          <t>1411655</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1577157</t>
+          <t>1411655</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1577157</t>
+          <t>1411655</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>378909</t>
+          <t>415993</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>358774</t>
+          <t>394249</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>398692</t>
+          <t>438592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>388673</t>
+          <t>433940</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>372410</t>
+          <t>415861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>404235</t>
+          <t>451171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>767581</t>
+          <t>849933</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>743027</t>
+          <t>823956</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>794285</t>
+          <t>877825</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,4%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>175341</t>
+          <t>186441</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>155558</t>
+          <t>163842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195476</t>
+          <t>208185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>145769</t>
+          <t>159507</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130207</t>
+          <t>142276</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162032</t>
+          <t>177586</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>321111</t>
+          <t>345948</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>294407</t>
+          <t>318056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>345665</t>
+          <t>371925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>554250</t>
+          <t>602434</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>554250</t>
+          <t>602434</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>554250</t>
+          <t>602434</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>534442</t>
+          <t>593447</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>534442</t>
+          <t>593447</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>534442</t>
+          <t>593447</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1088692</t>
+          <t>1195881</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1088692</t>
+          <t>1195881</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1088692</t>
+          <t>1195881</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>244351</t>
+          <t>270949</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>229592</t>
+          <t>255727</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>259505</t>
+          <t>286585</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>262731</t>
+          <t>289125</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>249135</t>
+          <t>275958</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>274939</t>
+          <t>301741</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>507082</t>
+          <t>560074</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>487102</t>
+          <t>538947</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>525633</t>
+          <t>582036</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,21%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>119086</t>
+          <t>131404</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>103932</t>
+          <t>115768</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133845</t>
+          <t>146626</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>127495</t>
+          <t>137526</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115287</t>
+          <t>124910</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>141091</t>
+          <t>150693</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>246581</t>
+          <t>268930</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>228030</t>
+          <t>246968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>266561</t>
+          <t>290057</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>363437</t>
+          <t>402353</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>363437</t>
+          <t>402353</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>363437</t>
+          <t>402353</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>390226</t>
+          <t>426651</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>390226</t>
+          <t>426651</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>390226</t>
+          <t>426651</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>753663</t>
+          <t>829004</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>753663</t>
+          <t>829004</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>753663</t>
+          <t>829004</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>195457</t>
+          <t>215956</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183074</t>
+          <t>202329</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>206445</t>
+          <t>227913</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,27 +11758,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>311528</t>
+          <t>340115</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>299137</t>
+          <t>326105</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>323513</t>
+          <t>353332</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>506985</t>
+          <t>556071</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>489099</t>
+          <t>537999</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>523289</t>
+          <t>574524</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,82%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>75288</t>
+          <t>81672</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64300</t>
+          <t>69715</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87671</t>
+          <t>95299</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,22 +11871,22 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>100740</t>
+          <t>110170</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>88755</t>
+          <t>96953</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>113131</t>
+          <t>124180</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>176028</t>
+          <t>191841</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>159724</t>
+          <t>173388</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>193914</t>
+          <t>209913</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>270745</t>
+          <t>297628</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>270745</t>
+          <t>297628</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>270745</t>
+          <t>297628</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>412268</t>
+          <t>450285</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>412268</t>
+          <t>450285</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>412268</t>
+          <t>450285</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>683013</t>
+          <t>747912</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>683013</t>
+          <t>747912</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>683013</t>
+          <t>747912</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1996471</t>
+          <t>2238205</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1494593</t>
+          <t>2176876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2170174</t>
+          <t>2301574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2120065</t>
+          <t>2392335</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1955444</t>
+          <t>2340477</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2194019</t>
+          <t>2443956</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4116536</t>
+          <t>4630539</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3527222</t>
+          <t>4547219</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4322024</t>
+          <t>4719049</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1414547</t>
+          <t>1241076</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1240844</t>
+          <t>1177707</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1916425</t>
+          <t>1302405</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1269893</t>
+          <t>1270276</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1195939</t>
+          <t>1218655</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1434514</t>
+          <t>1322134</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2684441</t>
+          <t>2511352</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2478953</t>
+          <t>2422842</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3273755</t>
+          <t>2594672</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3411018</t>
+          <t>3479281</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3411018</t>
+          <t>3479281</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3411018</t>
+          <t>3479281</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3389958</t>
+          <t>3662611</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3389958</t>
+          <t>3662611</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3389958</t>
+          <t>3662611</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6800977</t>
+          <t>7141891</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6800977</t>
+          <t>7141891</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6800977</t>
+          <t>7141891</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
